--- a/exercices/distribution_exercice_1.xlsx
+++ b/exercices/distribution_exercice_1.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEECAD1-EAF7-4A03-8774-C0C83C22C1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF59B8A-BAF5-4CDC-8009-FAD729716630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{DD14B73B-9482-43E6-98EF-428265CDF551}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="3" xr2:uid="{DD14B73B-9482-43E6-98EF-428265CDF551}"/>
   </bookViews>
   <sheets>
-    <sheet name="lorenz_gini" sheetId="1" r:id="rId1"/>
-    <sheet name="theil" sheetId="2" r:id="rId2"/>
+    <sheet name="lorenz_gini_CH" sheetId="1" r:id="rId1"/>
+    <sheet name="theil_CH" sheetId="2" r:id="rId2"/>
+    <sheet name="lorenz_gini_GE" sheetId="3" r:id="rId3"/>
+    <sheet name="theil_GE" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -347,23 +349,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -371,18 +358,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -390,12 +370,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -404,15 +378,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -432,6 +397,53 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -775,115 +787,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="2" t="s">
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="4" t="s">
+      <c r="K1" s="30"/>
+      <c r="L1" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
     </row>
     <row r="2" spans="1:17" ht="203" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="9"/>
-      <c r="L2" s="10" t="s">
+      <c r="K2" s="34"/>
+      <c r="L2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="7">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="2">
         <v>0</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="2">
         <v>0</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="2">
         <v>0</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="40">
         <v>0</v>
       </c>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="7"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" s="13">
-        <v>0</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="5">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5">
         <v>20000</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="21"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="11"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -892,19 +904,19 @@
       <c r="B5">
         <v>25000</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="21"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="11"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
@@ -913,19 +925,19 @@
       <c r="B6">
         <v>30000</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="21"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="11"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -934,19 +946,19 @@
       <c r="B7">
         <v>35000</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="21"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="11"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -955,19 +967,19 @@
       <c r="B8">
         <v>40000</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="21"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="11"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -976,19 +988,19 @@
       <c r="B9">
         <v>45000</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="21"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="11"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -997,19 +1009,19 @@
       <c r="B10">
         <v>50000</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="21"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="43"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="11"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
@@ -1018,19 +1030,19 @@
       <c r="B11">
         <v>55000</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="21"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="11"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
@@ -1039,19 +1051,19 @@
       <c r="B12">
         <v>60000</v>
       </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="19"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="21"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="43"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="11"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
@@ -1060,19 +1072,19 @@
       <c r="B13">
         <v>65000</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="20"/>
-      <c r="O13" s="21"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="11"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
@@ -1081,19 +1093,19 @@
       <c r="B14">
         <v>70000</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="21"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="11"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
@@ -1102,19 +1114,19 @@
       <c r="B15">
         <v>75000</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="21"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="44"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="11"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
@@ -1123,19 +1135,19 @@
       <c r="B16">
         <v>80000</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="21"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="11"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17">
@@ -1144,19 +1156,19 @@
       <c r="B17">
         <v>85000</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="21"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="44"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="11"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18">
@@ -1165,19 +1177,19 @@
       <c r="B18">
         <v>90000</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="20"/>
-      <c r="O18" s="21"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="44"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="11"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19">
@@ -1186,19 +1198,19 @@
       <c r="B19">
         <v>95000</v>
       </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="21"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="41"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="11"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20">
@@ -1207,19 +1219,19 @@
       <c r="B20">
         <v>100000</v>
       </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="21"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="11"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21">
@@ -1228,19 +1240,19 @@
       <c r="B21">
         <v>120000</v>
       </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="21"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="11"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22">
@@ -1249,19 +1261,19 @@
       <c r="B22">
         <v>150000</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="21"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="11"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23">
@@ -1270,19 +1282,19 @@
       <c r="B23">
         <v>200000</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="21"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="11"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24">
@@ -1291,19 +1303,19 @@
       <c r="B24">
         <v>300000</v>
       </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="21"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="41"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="44"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="11"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25">
@@ -1312,19 +1324,19 @@
       <c r="B25">
         <v>400000</v>
       </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="17"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="19"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="21"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="44"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="11"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26">
@@ -1333,19 +1345,19 @@
       <c r="B26">
         <v>500000</v>
       </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="19"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="21"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="44"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="11"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27">
@@ -1354,19 +1366,19 @@
       <c r="B27">
         <v>1000000</v>
       </c>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="17"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="19"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="21"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="44"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="11"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28">
@@ -1375,19 +1387,19 @@
       <c r="B28">
         <v>2000000</v>
       </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="17"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="19"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="21"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="44"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="11"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29">
@@ -1396,73 +1408,99 @@
       <c r="B29" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="17"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="20"/>
-      <c r="O29" s="21"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="11"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="15"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="39"/>
+      <c r="K30" s="39"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N31" t="s">
         <v>19</v>
       </c>
-      <c r="O31" s="25"/>
+      <c r="O31" s="15"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>20</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="10">
         <f>SUM(C4:C29)</f>
         <v>0</v>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="10">
         <f>SUM(D4:D29)</f>
         <v>0</v>
       </c>
       <c r="I32" t="s">
         <v>21</v>
       </c>
-      <c r="J32" s="15"/>
+      <c r="J32" s="7"/>
       <c r="N32" t="s">
         <v>22</v>
       </c>
-      <c r="O32" s="25"/>
+      <c r="O32" s="15"/>
     </row>
     <row r="33" spans="9:10" x14ac:dyDescent="0.35">
       <c r="I33" t="s">
         <v>1</v>
       </c>
-      <c r="J33" s="15"/>
+      <c r="J33" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="30">
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="J19:K19"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="L1:Q1"/>
     <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1478,57 +1516,57 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="1:13" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="26" t="s">
+      <c r="I2" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="27"/>
-      <c r="K2" s="28"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="37"/>
     </row>
     <row r="3" spans="1:13" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="I3" s="29" t="s">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="I3" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="30" t="s">
+      <c r="J3" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="31" t="s">
+      <c r="K3" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="40"/>
+      <c r="M3" s="27"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="13">
+      <c r="A4" s="5">
         <v>0</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="5">
         <v>20000</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="33"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="20"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
@@ -1537,12 +1575,12 @@
       <c r="B5">
         <v>25000</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="23"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="35"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="13"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="22"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
@@ -1551,12 +1589,12 @@
       <c r="B6">
         <v>30000</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="23"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="35"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="13"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="22"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -1565,12 +1603,12 @@
       <c r="B7">
         <v>35000</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="35"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="13"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="22"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -1579,12 +1617,12 @@
       <c r="B8">
         <v>40000</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="23"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="35"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="13"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="22"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -1593,12 +1631,12 @@
       <c r="B9">
         <v>45000</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="23"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="35"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="13"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="22"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -1607,12 +1645,12 @@
       <c r="B10">
         <v>50000</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="23"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="35"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="13"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="22"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
@@ -1621,12 +1659,12 @@
       <c r="B11">
         <v>55000</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="23"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="35"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="13"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="22"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
@@ -1635,12 +1673,12 @@
       <c r="B12">
         <v>60000</v>
       </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="35"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="13"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="22"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
@@ -1649,12 +1687,12 @@
       <c r="B13">
         <v>65000</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="23"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="35"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="22"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
@@ -1663,12 +1701,12 @@
       <c r="B14">
         <v>70000</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="35"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="13"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="22"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
@@ -1677,12 +1715,12 @@
       <c r="B15">
         <v>75000</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="23"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="35"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="13"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="22"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
@@ -1691,12 +1729,12 @@
       <c r="B16">
         <v>80000</v>
       </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="23"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="35"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="22"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17">
@@ -1705,12 +1743,12 @@
       <c r="B17">
         <v>85000</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="23"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="35"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="13"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="22"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18">
@@ -1719,12 +1757,12 @@
       <c r="B18">
         <v>90000</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="23"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="35"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="13"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="22"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19">
@@ -1733,12 +1771,12 @@
       <c r="B19">
         <v>95000</v>
       </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="23"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="35"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="13"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="22"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20">
@@ -1747,12 +1785,12 @@
       <c r="B20">
         <v>100000</v>
       </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="23"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="35"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="13"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="22"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21">
@@ -1761,12 +1799,12 @@
       <c r="B21">
         <v>120000</v>
       </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="23"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="35"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="13"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="22"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22">
@@ -1775,12 +1813,12 @@
       <c r="B22">
         <v>150000</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="23"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="35"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="13"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="22"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23">
@@ -1789,12 +1827,12 @@
       <c r="B23">
         <v>200000</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="23"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="35"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="13"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="22"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24">
@@ -1803,12 +1841,12 @@
       <c r="B24">
         <v>300000</v>
       </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="23"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="34"/>
-      <c r="K24" s="35"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="13"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="22"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25">
@@ -1817,12 +1855,12 @@
       <c r="B25">
         <v>400000</v>
       </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="23"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="34"/>
-      <c r="K25" s="35"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="13"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="22"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26">
@@ -1831,12 +1869,12 @@
       <c r="B26">
         <v>500000</v>
       </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="23"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="35"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="13"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="22"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27">
@@ -1845,12 +1883,12 @@
       <c r="B27">
         <v>1000000</v>
       </c>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="23"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="34"/>
-      <c r="K27" s="35"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="13"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="22"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28">
@@ -1859,12 +1897,12 @@
       <c r="B28">
         <v>2000000</v>
       </c>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="23"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="35"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="13"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="22"/>
     </row>
     <row r="29" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29">
@@ -1873,28 +1911,28 @@
       <c r="B29" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="23"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="36"/>
-      <c r="K29" s="37"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="13"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="24"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B30" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="23"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="13"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="K31" s="38" t="s">
+      <c r="K31" s="25" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="K32" s="39">
+      <c r="K32" s="26">
         <f>SUM(K4:K29)</f>
         <v>0</v>
       </c>
@@ -1905,4 +1943,22 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1140C43B-C920-4D11-817E-BD364D3B388D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A3719E-7FC9-4C3A-82D0-D449E932CCBB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/exercices/distribution_exercice_1.xlsx
+++ b/exercices/distribution_exercice_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF59B8A-BAF5-4CDC-8009-FAD729716630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6436F00-80C7-4DB5-8D8B-480F46041C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="3" xr2:uid="{DD14B73B-9482-43E6-98EF-428265CDF551}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{DD14B73B-9482-43E6-98EF-428265CDF551}"/>
   </bookViews>
   <sheets>
     <sheet name="lorenz_gini_CH" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="26">
   <si>
     <t>Courbe de Lorenz</t>
   </si>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t>u.m./et plus</t>
-  </si>
-  <si>
-    <t>Total / Totale</t>
   </si>
   <si>
     <t>Part du 0.1%</t>
@@ -398,6 +395,23 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -427,23 +441,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -787,24 +784,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="29" t="s">
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="30"/>
-      <c r="L1" s="31" t="s">
+      <c r="K1" s="37"/>
+      <c r="L1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
     </row>
     <row r="2" spans="1:17" ht="203" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -834,10 +831,10 @@
       <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="33" t="s">
+      <c r="J2" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="34"/>
+      <c r="K2" s="41"/>
       <c r="L2" s="3" t="s">
         <v>13</v>
       </c>
@@ -866,12 +863,12 @@
       <c r="H3" s="2">
         <v>0</v>
       </c>
-      <c r="I3" s="40">
+      <c r="I3" s="30">
         <v>0</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="42"/>
+      <c r="L3" s="32"/>
       <c r="M3" s="2"/>
       <c r="N3" s="4"/>
       <c r="O3" s="2"/>
@@ -888,10 +885,10 @@
       <c r="E4" s="5"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="38"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="44"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="34"/>
       <c r="L4" s="8"/>
       <c r="M4" s="9"/>
       <c r="N4" s="10"/>
@@ -909,10 +906,10 @@
       <c r="E5" s="13"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="44"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="34"/>
       <c r="L5" s="14"/>
       <c r="M5" s="9"/>
       <c r="N5" s="10"/>
@@ -930,10 +927,10 @@
       <c r="E6" s="13"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="44"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="34"/>
       <c r="L6" s="14"/>
       <c r="M6" s="9"/>
       <c r="N6" s="10"/>
@@ -951,10 +948,10 @@
       <c r="E7" s="13"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="44"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="34"/>
       <c r="L7" s="14"/>
       <c r="M7" s="9"/>
       <c r="N7" s="10"/>
@@ -972,10 +969,10 @@
       <c r="E8" s="13"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="44"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="34"/>
       <c r="L8" s="14"/>
       <c r="M8" s="9"/>
       <c r="N8" s="10"/>
@@ -993,10 +990,10 @@
       <c r="E9" s="13"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="44"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="34"/>
       <c r="L9" s="14"/>
       <c r="M9" s="9"/>
       <c r="N9" s="10"/>
@@ -1014,10 +1011,10 @@
       <c r="E10" s="13"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="41"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="44"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="34"/>
       <c r="L10" s="14"/>
       <c r="M10" s="9"/>
       <c r="N10" s="10"/>
@@ -1035,10 +1032,10 @@
       <c r="E11" s="13"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="44"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="34"/>
       <c r="L11" s="14"/>
       <c r="M11" s="9"/>
       <c r="N11" s="10"/>
@@ -1056,10 +1053,10 @@
       <c r="E12" s="13"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="44"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="34"/>
       <c r="L12" s="14"/>
       <c r="M12" s="9"/>
       <c r="N12" s="10"/>
@@ -1077,10 +1074,10 @@
       <c r="E13" s="13"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="44"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="34"/>
       <c r="L13" s="14"/>
       <c r="M13" s="9"/>
       <c r="N13" s="10"/>
@@ -1098,10 +1095,10 @@
       <c r="E14" s="13"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="44"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="34"/>
       <c r="L14" s="14"/>
       <c r="M14" s="9"/>
       <c r="N14" s="10"/>
@@ -1119,10 +1116,10 @@
       <c r="E15" s="13"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="44"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="34"/>
       <c r="L15" s="14"/>
       <c r="M15" s="9"/>
       <c r="N15" s="10"/>
@@ -1140,10 +1137,10 @@
       <c r="E16" s="13"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="44"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="34"/>
       <c r="L16" s="14"/>
       <c r="M16" s="9"/>
       <c r="N16" s="10"/>
@@ -1161,10 +1158,10 @@
       <c r="E17" s="13"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="44"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="34"/>
       <c r="L17" s="14"/>
       <c r="M17" s="9"/>
       <c r="N17" s="10"/>
@@ -1182,10 +1179,10 @@
       <c r="E18" s="13"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="44"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="34"/>
       <c r="L18" s="14"/>
       <c r="M18" s="9"/>
       <c r="N18" s="10"/>
@@ -1203,10 +1200,10 @@
       <c r="E19" s="13"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="44"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="34"/>
       <c r="L19" s="14"/>
       <c r="M19" s="9"/>
       <c r="N19" s="10"/>
@@ -1224,10 +1221,10 @@
       <c r="E20" s="13"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="44"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="34"/>
       <c r="L20" s="14"/>
       <c r="M20" s="9"/>
       <c r="N20" s="10"/>
@@ -1245,10 +1242,10 @@
       <c r="E21" s="13"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="44"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="34"/>
       <c r="L21" s="14"/>
       <c r="M21" s="9"/>
       <c r="N21" s="10"/>
@@ -1266,10 +1263,10 @@
       <c r="E22" s="13"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="44"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="34"/>
       <c r="L22" s="14"/>
       <c r="M22" s="9"/>
       <c r="N22" s="10"/>
@@ -1287,10 +1284,10 @@
       <c r="E23" s="13"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="44"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="34"/>
       <c r="L23" s="14"/>
       <c r="M23" s="9"/>
       <c r="N23" s="10"/>
@@ -1308,10 +1305,10 @@
       <c r="E24" s="13"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="43"/>
-      <c r="K24" s="44"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="34"/>
       <c r="L24" s="14"/>
       <c r="M24" s="9"/>
       <c r="N24" s="10"/>
@@ -1329,10 +1326,10 @@
       <c r="E25" s="13"/>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="44"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="34"/>
       <c r="L25" s="14"/>
       <c r="M25" s="9"/>
       <c r="N25" s="10"/>
@@ -1350,10 +1347,10 @@
       <c r="E26" s="13"/>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="43"/>
-      <c r="K26" s="44"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="34"/>
       <c r="L26" s="14"/>
       <c r="M26" s="9"/>
       <c r="N26" s="10"/>
@@ -1371,10 +1368,10 @@
       <c r="E27" s="13"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="43"/>
-      <c r="K27" s="44"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="34"/>
       <c r="L27" s="14"/>
       <c r="M27" s="9"/>
       <c r="N27" s="10"/>
@@ -1392,10 +1389,10 @@
       <c r="E28" s="13"/>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="43"/>
-      <c r="K28" s="44"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="34"/>
       <c r="L28" s="14"/>
       <c r="M28" s="9"/>
       <c r="N28" s="10"/>
@@ -1413,38 +1410,35 @@
       <c r="E29" s="13"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="43"/>
-      <c r="K29" s="44"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="34"/>
       <c r="L29" s="14"/>
       <c r="M29" s="9"/>
       <c r="N29" s="10"/>
       <c r="O29" s="11"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B30" t="s">
-        <v>18</v>
-      </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
       <c r="E30" s="13"/>
-      <c r="F30" s="39"/>
-      <c r="G30" s="39"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
       <c r="H30" s="27"/>
       <c r="I30" s="27"/>
-      <c r="J30" s="39"/>
-      <c r="K30" s="39"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O31" s="15"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C32" s="10">
         <f>SUM(C4:C29)</f>
@@ -1455,11 +1449,11 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J32" s="7"/>
       <c r="N32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O32" s="15"/>
     </row>
@@ -1471,36 +1465,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="J24:K24"/>
     <mergeCell ref="J25:K25"/>
     <mergeCell ref="J26:K26"/>
     <mergeCell ref="J27:K27"/>
     <mergeCell ref="J28:K28"/>
     <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:Q1"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1531,11 +1525,11 @@
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="36"/>
-      <c r="K2" s="37"/>
+      <c r="I2" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="43"/>
+      <c r="K2" s="44"/>
     </row>
     <row r="3" spans="1:13" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
@@ -1544,13 +1538,13 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="I3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="K3" s="18" t="s">
         <v>25</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>26</v>
       </c>
       <c r="M3" s="27"/>
     </row>
@@ -1919,16 +1913,13 @@
       <c r="K29" s="24"/>
     </row>
     <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" t="s">
-        <v>18</v>
-      </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
       <c r="E30" s="13"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="K31" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1947,18 +1938,1161 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1140C43B-C920-4D11-817E-BD364D3B388D}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="9" max="9" width="19.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="F1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="37"/>
+      <c r="L1" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+    </row>
+    <row r="2" spans="1:17" ht="203" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="41"/>
+      <c r="L2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="30">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="5">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5">
+        <v>20000</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="11"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>20001</v>
+      </c>
+      <c r="B5">
+        <v>25000</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="11"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>25001</v>
+      </c>
+      <c r="B6">
+        <v>30000</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="11"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>30001</v>
+      </c>
+      <c r="B7">
+        <v>35000</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="11"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>35001</v>
+      </c>
+      <c r="B8">
+        <v>40000</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="11"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>40001</v>
+      </c>
+      <c r="B9">
+        <v>45000</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="11"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>45001</v>
+      </c>
+      <c r="B10">
+        <v>50000</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="11"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>50001</v>
+      </c>
+      <c r="B11">
+        <v>55000</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="11"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>55001</v>
+      </c>
+      <c r="B12">
+        <v>60000</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="11"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>60001</v>
+      </c>
+      <c r="B13">
+        <v>65000</v>
+      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="11"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>65001</v>
+      </c>
+      <c r="B14">
+        <v>70000</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="11"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>70001</v>
+      </c>
+      <c r="B15">
+        <v>75000</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="11"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>75001</v>
+      </c>
+      <c r="B16">
+        <v>80000</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="11"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>80001</v>
+      </c>
+      <c r="B17">
+        <v>85000</v>
+      </c>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="11"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>85001</v>
+      </c>
+      <c r="B18">
+        <v>90000</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="11"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>90001</v>
+      </c>
+      <c r="B19">
+        <v>95000</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="11"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>95001</v>
+      </c>
+      <c r="B20">
+        <v>100000</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="11"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>100001</v>
+      </c>
+      <c r="B21">
+        <v>120000</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="11"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>120001</v>
+      </c>
+      <c r="B22">
+        <v>150000</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="11"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>150001</v>
+      </c>
+      <c r="B23">
+        <v>200000</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="11"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>200001</v>
+      </c>
+      <c r="B24">
+        <v>300000</v>
+      </c>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="11"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>300001</v>
+      </c>
+      <c r="B25">
+        <v>400000</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="11"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>400001</v>
+      </c>
+      <c r="B26">
+        <v>500000</v>
+      </c>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="11"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>500001</v>
+      </c>
+      <c r="B27">
+        <v>1000000</v>
+      </c>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="11"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>1000001</v>
+      </c>
+      <c r="B28">
+        <v>2000000</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="11"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>2000001</v>
+      </c>
+      <c r="B29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="11"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N31" t="s">
+        <v>18</v>
+      </c>
+      <c r="O31" s="15"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="10">
+        <f>SUM(C4:C29)</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="10">
+        <f>SUM(D4:D29)</f>
+        <v>0</v>
+      </c>
+      <c r="I32" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" s="7"/>
+      <c r="N32" t="s">
+        <v>21</v>
+      </c>
+      <c r="O32" s="15"/>
+    </row>
+    <row r="33" spans="9:10" x14ac:dyDescent="0.35">
+      <c r="I33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J33" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A3719E-7FC9-4C3A-82D0-D449E932CCBB}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="11" max="11" width="13.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:13" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="43"/>
+      <c r="K2" s="44"/>
+    </row>
+    <row r="3" spans="1:13" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="I3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="27"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="5">
+        <v>0</v>
+      </c>
+      <c r="B4" s="5">
+        <v>20000</v>
+      </c>
+      <c r="C4" s="6"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="20"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>20001</v>
+      </c>
+      <c r="B5">
+        <v>25000</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="13"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="22"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>25001</v>
+      </c>
+      <c r="B6">
+        <v>30000</v>
+      </c>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="13"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="22"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>30001</v>
+      </c>
+      <c r="B7">
+        <v>35000</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="13"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="22"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>35001</v>
+      </c>
+      <c r="B8">
+        <v>40000</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="13"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="22"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>40001</v>
+      </c>
+      <c r="B9">
+        <v>45000</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="13"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="22"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>45001</v>
+      </c>
+      <c r="B10">
+        <v>50000</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="13"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="22"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>50001</v>
+      </c>
+      <c r="B11">
+        <v>55000</v>
+      </c>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="13"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="22"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>55001</v>
+      </c>
+      <c r="B12">
+        <v>60000</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="13"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="22"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>60001</v>
+      </c>
+      <c r="B13">
+        <v>65000</v>
+      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="22"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>65001</v>
+      </c>
+      <c r="B14">
+        <v>70000</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="13"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="22"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>70001</v>
+      </c>
+      <c r="B15">
+        <v>75000</v>
+      </c>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="13"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="22"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>75001</v>
+      </c>
+      <c r="B16">
+        <v>80000</v>
+      </c>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="22"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>80001</v>
+      </c>
+      <c r="B17">
+        <v>85000</v>
+      </c>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="13"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="22"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>85001</v>
+      </c>
+      <c r="B18">
+        <v>90000</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="13"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="22"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>90001</v>
+      </c>
+      <c r="B19">
+        <v>95000</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="13"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="22"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>95001</v>
+      </c>
+      <c r="B20">
+        <v>100000</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="13"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="22"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>100001</v>
+      </c>
+      <c r="B21">
+        <v>120000</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="13"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="22"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>120001</v>
+      </c>
+      <c r="B22">
+        <v>150000</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="13"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="22"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>150001</v>
+      </c>
+      <c r="B23">
+        <v>200000</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="13"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="22"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>200001</v>
+      </c>
+      <c r="B24">
+        <v>300000</v>
+      </c>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="13"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="22"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>300001</v>
+      </c>
+      <c r="B25">
+        <v>400000</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="13"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="22"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>400001</v>
+      </c>
+      <c r="B26">
+        <v>500000</v>
+      </c>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="13"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="22"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>500001</v>
+      </c>
+      <c r="B27">
+        <v>1000000</v>
+      </c>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="13"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="22"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>1000001</v>
+      </c>
+      <c r="B28">
+        <v>2000000</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="13"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="22"/>
+    </row>
+    <row r="29" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>2000001</v>
+      </c>
+      <c r="B29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="13"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="24"/>
+    </row>
+    <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="13"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K31" s="25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K32" s="26">
+        <f>SUM(K4:K29)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I2:K2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/exercices/distribution_exercice_1.xlsx
+++ b/exercices/distribution_exercice_1.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\les-mesures-de-l-conomie\exercices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6436F00-80C7-4DB5-8D8B-480F46041C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B73F7D38-F7C4-496D-BD90-C2DB24B41FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{DD14B73B-9482-43E6-98EF-428265CDF551}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{DD14B73B-9482-43E6-98EF-428265CDF551}"/>
   </bookViews>
   <sheets>
     <sheet name="lorenz_gini_CH" sheetId="1" r:id="rId1"/>
-    <sheet name="theil_CH" sheetId="2" r:id="rId2"/>
-    <sheet name="lorenz_gini_GE" sheetId="3" r:id="rId3"/>
+    <sheet name="lorenz_gini_GE" sheetId="3" r:id="rId2"/>
+    <sheet name="theil_CH" sheetId="2" r:id="rId3"/>
     <sheet name="theil_GE" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="27">
   <si>
     <t>Courbe de Lorenz</t>
   </si>
@@ -98,9 +98,6 @@
     <t>u.m./et plus</t>
   </si>
   <si>
-    <t>Part du 0.1%</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
@@ -120,6 +117,12 @@
   </si>
   <si>
     <t>Indice theil du groupe</t>
+  </si>
+  <si>
+    <t>Part du 10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copiez-collez vos données dans les cases grises, le reste est à calculer </t>
   </si>
 </sst>
 </file>
@@ -154,7 +157,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -206,6 +209,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -346,7 +355,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -440,6 +449,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -784,6 +804,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
       <c r="F1" s="35" t="s">
         <v>0</v>
       </c>
@@ -874,14 +901,14 @@
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5">
+      <c r="A4" s="45">
+        <v>0</v>
+      </c>
+      <c r="B4" s="45">
         <v>20000</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="45"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -895,14 +922,14 @@
       <c r="O4" s="11"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A5">
+      <c r="A5" s="47">
         <v>20001</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="47">
         <v>25000</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
       <c r="E5" s="13"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
@@ -916,14 +943,14 @@
       <c r="O5" s="11"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A6">
+      <c r="A6" s="47">
         <v>25001</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="47">
         <v>30000</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
       <c r="E6" s="13"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
@@ -937,14 +964,14 @@
       <c r="O6" s="11"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A7">
+      <c r="A7" s="47">
         <v>30001</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="47">
         <v>35000</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
       <c r="E7" s="13"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
@@ -958,14 +985,14 @@
       <c r="O7" s="11"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A8">
+      <c r="A8" s="47">
         <v>35001</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="47">
         <v>40000</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
       <c r="E8" s="13"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
@@ -979,14 +1006,14 @@
       <c r="O8" s="11"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A9">
+      <c r="A9" s="47">
         <v>40001</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="47">
         <v>45000</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
       <c r="E9" s="13"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
@@ -1000,14 +1027,14 @@
       <c r="O9" s="11"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A10">
+      <c r="A10" s="47">
         <v>45001</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="47">
         <v>50000</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
       <c r="E10" s="13"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
@@ -1021,14 +1048,14 @@
       <c r="O10" s="11"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A11">
+      <c r="A11" s="47">
         <v>50001</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="47">
         <v>55000</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
       <c r="E11" s="13"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1042,14 +1069,14 @@
       <c r="O11" s="11"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A12">
+      <c r="A12" s="47">
         <v>55001</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="47">
         <v>60000</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
       <c r="E12" s="13"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
@@ -1063,14 +1090,14 @@
       <c r="O12" s="11"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A13">
+      <c r="A13" s="47">
         <v>60001</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="47">
         <v>65000</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
       <c r="E13" s="13"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -1084,14 +1111,14 @@
       <c r="O13" s="11"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A14">
+      <c r="A14" s="47">
         <v>65001</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="47">
         <v>70000</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
       <c r="E14" s="13"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -1105,14 +1132,14 @@
       <c r="O14" s="11"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A15">
+      <c r="A15" s="47">
         <v>70001</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="47">
         <v>75000</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
       <c r="E15" s="13"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
@@ -1126,14 +1153,14 @@
       <c r="O15" s="11"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A16">
+      <c r="A16" s="47">
         <v>75001</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="47">
         <v>80000</v>
       </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
       <c r="E16" s="13"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1147,14 +1174,14 @@
       <c r="O16" s="11"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A17">
+      <c r="A17" s="47">
         <v>80001</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="47">
         <v>85000</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
       <c r="E17" s="13"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
@@ -1168,14 +1195,14 @@
       <c r="O17" s="11"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A18">
+      <c r="A18" s="47">
         <v>85001</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="47">
         <v>90000</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
       <c r="E18" s="13"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
@@ -1189,14 +1216,14 @@
       <c r="O18" s="11"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A19">
+      <c r="A19" s="47">
         <v>90001</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="47">
         <v>95000</v>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
       <c r="E19" s="13"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
@@ -1210,14 +1237,14 @@
       <c r="O19" s="11"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A20">
+      <c r="A20" s="47">
         <v>95001</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="47">
         <v>100000</v>
       </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
       <c r="E20" s="13"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
@@ -1231,14 +1258,14 @@
       <c r="O20" s="11"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A21">
+      <c r="A21" s="47">
         <v>100001</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="47">
         <v>120000</v>
       </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
       <c r="E21" s="13"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -1252,14 +1279,14 @@
       <c r="O21" s="11"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A22">
+      <c r="A22" s="47">
         <v>120001</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="47">
         <v>150000</v>
       </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
       <c r="E22" s="13"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
@@ -1273,14 +1300,14 @@
       <c r="O22" s="11"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A23">
+      <c r="A23" s="47">
         <v>150001</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="47">
         <v>200000</v>
       </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
       <c r="E23" s="13"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
@@ -1294,14 +1321,14 @@
       <c r="O23" s="11"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A24">
+      <c r="A24" s="47">
         <v>200001</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="47">
         <v>300000</v>
       </c>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
       <c r="E24" s="13"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
@@ -1315,14 +1342,14 @@
       <c r="O24" s="11"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A25">
+      <c r="A25" s="47">
         <v>300001</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="47">
         <v>400000</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
       <c r="E25" s="13"/>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
@@ -1336,14 +1363,14 @@
       <c r="O25" s="11"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A26">
+      <c r="A26" s="47">
         <v>400001</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="47">
         <v>500000</v>
       </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
       <c r="E26" s="13"/>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
@@ -1357,14 +1384,14 @@
       <c r="O26" s="11"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A27">
+      <c r="A27" s="47">
         <v>500001</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="47">
         <v>1000000</v>
       </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
       <c r="E27" s="13"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
@@ -1378,14 +1405,14 @@
       <c r="O27" s="11"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A28">
+      <c r="A28" s="47">
         <v>1000001</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="47">
         <v>2000000</v>
       </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
       <c r="E28" s="13"/>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
@@ -1399,14 +1426,14 @@
       <c r="O28" s="11"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A29">
+      <c r="A29" s="47">
         <v>2000001</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="48"/>
       <c r="E29" s="13"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
@@ -1432,13 +1459,13 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="N31" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O31" s="15"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C32" s="10">
         <f>SUM(C4:C29)</f>
@@ -1449,11 +1476,11 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J32" s="7"/>
       <c r="N32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O32" s="15"/>
     </row>
@@ -1464,25 +1491,760 @@
       <c r="J33" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J9:K9"/>
     <mergeCell ref="J10:K10"/>
     <mergeCell ref="J11:K11"/>
     <mergeCell ref="J12:K12"/>
     <mergeCell ref="J13:K13"/>
     <mergeCell ref="J14:K14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1140C43B-C920-4D11-817E-BD364D3B388D}">
+  <dimension ref="A1:Q33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="9" max="9" width="19.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A1" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="37"/>
+      <c r="L1" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+    </row>
+    <row r="2" spans="1:17" ht="203" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="41"/>
+      <c r="L2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="30">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="45">
+        <v>0</v>
+      </c>
+      <c r="B4" s="45">
+        <v>20000</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="11"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A5" s="47">
+        <v>20001</v>
+      </c>
+      <c r="B5" s="47">
+        <v>25000</v>
+      </c>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="11"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A6" s="47">
+        <v>25001</v>
+      </c>
+      <c r="B6" s="47">
+        <v>30000</v>
+      </c>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="11"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A7" s="47">
+        <v>30001</v>
+      </c>
+      <c r="B7" s="47">
+        <v>35000</v>
+      </c>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="11"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A8" s="47">
+        <v>35001</v>
+      </c>
+      <c r="B8" s="47">
+        <v>40000</v>
+      </c>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="11"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9" s="47">
+        <v>40001</v>
+      </c>
+      <c r="B9" s="47">
+        <v>45000</v>
+      </c>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="11"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A10" s="47">
+        <v>45001</v>
+      </c>
+      <c r="B10" s="47">
+        <v>50000</v>
+      </c>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="11"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A11" s="47">
+        <v>50001</v>
+      </c>
+      <c r="B11" s="47">
+        <v>55000</v>
+      </c>
+      <c r="C11" s="48"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="11"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A12" s="47">
+        <v>55001</v>
+      </c>
+      <c r="B12" s="47">
+        <v>60000</v>
+      </c>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="11"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A13" s="47">
+        <v>60001</v>
+      </c>
+      <c r="B13" s="47">
+        <v>65000</v>
+      </c>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="11"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A14" s="47">
+        <v>65001</v>
+      </c>
+      <c r="B14" s="47">
+        <v>70000</v>
+      </c>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="11"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A15" s="47">
+        <v>70001</v>
+      </c>
+      <c r="B15" s="47">
+        <v>75000</v>
+      </c>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="11"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A16" s="47">
+        <v>75001</v>
+      </c>
+      <c r="B16" s="47">
+        <v>80000</v>
+      </c>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="11"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17" s="47">
+        <v>80001</v>
+      </c>
+      <c r="B17" s="47">
+        <v>85000</v>
+      </c>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="11"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" s="47">
+        <v>85001</v>
+      </c>
+      <c r="B18" s="47">
+        <v>90000</v>
+      </c>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="11"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19" s="47">
+        <v>90001</v>
+      </c>
+      <c r="B19" s="47">
+        <v>95000</v>
+      </c>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="11"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" s="47">
+        <v>95001</v>
+      </c>
+      <c r="B20" s="47">
+        <v>100000</v>
+      </c>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="11"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" s="47">
+        <v>100001</v>
+      </c>
+      <c r="B21" s="47">
+        <v>120000</v>
+      </c>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="11"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22" s="47">
+        <v>120001</v>
+      </c>
+      <c r="B22" s="47">
+        <v>150000</v>
+      </c>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="11"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23" s="47">
+        <v>150001</v>
+      </c>
+      <c r="B23" s="47">
+        <v>200000</v>
+      </c>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="11"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24" s="47">
+        <v>200001</v>
+      </c>
+      <c r="B24" s="47">
+        <v>300000</v>
+      </c>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="11"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25" s="47">
+        <v>300001</v>
+      </c>
+      <c r="B25" s="47">
+        <v>400000</v>
+      </c>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="11"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A26" s="47">
+        <v>400001</v>
+      </c>
+      <c r="B26" s="47">
+        <v>500000</v>
+      </c>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="11"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A27" s="47">
+        <v>500001</v>
+      </c>
+      <c r="B27" s="47">
+        <v>1000000</v>
+      </c>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="11"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A28" s="47">
+        <v>1000001</v>
+      </c>
+      <c r="B28" s="47">
+        <v>2000000</v>
+      </c>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="11"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A29" s="47">
+        <v>2000001</v>
+      </c>
+      <c r="B29" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="48"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="11"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="27"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="N31" t="s">
+        <v>25</v>
+      </c>
+      <c r="O31" s="15"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="10">
+        <f>SUM(C4:C29)</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="10">
+        <f>SUM(D4:D29)</f>
+        <v>0</v>
+      </c>
+      <c r="I32" t="s">
+        <v>19</v>
+      </c>
+      <c r="J32" s="7"/>
+      <c r="N32" t="s">
+        <v>20</v>
+      </c>
+      <c r="O32" s="15"/>
+    </row>
+    <row r="33" spans="9:10" x14ac:dyDescent="0.35">
+      <c r="I33" t="s">
+        <v>1</v>
+      </c>
+      <c r="J33" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="31">
     <mergeCell ref="J5:K5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="F1:I1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="L1:Q1"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="J4:K4"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="J14:K14"/>
     <mergeCell ref="J15:K15"/>
     <mergeCell ref="J16:K16"/>
-    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J29:K29"/>
     <mergeCell ref="J18:K18"/>
     <mergeCell ref="J19:K19"/>
     <mergeCell ref="J20:K20"/>
@@ -1494,13 +2256,12 @@
     <mergeCell ref="J26:K26"/>
     <mergeCell ref="J27:K27"/>
     <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85802387-CEAC-4D1F-B06A-F87232343DD6}">
   <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1526,7 +2287,7 @@
         <v>7</v>
       </c>
       <c r="I2" s="42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J2" s="43"/>
       <c r="K2" s="44"/>
@@ -1538,13 +2299,13 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="I3" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="K3" s="18" t="s">
         <v>24</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>25</v>
       </c>
       <c r="M3" s="27"/>
     </row>
@@ -1919,7 +2680,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="K31" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1931,731 +2692,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="I2:K2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1140C43B-C920-4D11-817E-BD364D3B388D}">
-  <dimension ref="A1:Q33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="9" max="9" width="19.453125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="F1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="37"/>
-      <c r="L1" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-    </row>
-    <row r="2" spans="1:17" ht="203" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="41"/>
-      <c r="L2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="30">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="2"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5">
-        <v>20000</v>
-      </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="11"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>20001</v>
-      </c>
-      <c r="B5">
-        <v>25000</v>
-      </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="11"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>25001</v>
-      </c>
-      <c r="B6">
-        <v>30000</v>
-      </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="11"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>30001</v>
-      </c>
-      <c r="B7">
-        <v>35000</v>
-      </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="11"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>35001</v>
-      </c>
-      <c r="B8">
-        <v>40000</v>
-      </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="28"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="11"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>40001</v>
-      </c>
-      <c r="B9">
-        <v>45000</v>
-      </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="11"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>45001</v>
-      </c>
-      <c r="B10">
-        <v>50000</v>
-      </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="11"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>50001</v>
-      </c>
-      <c r="B11">
-        <v>55000</v>
-      </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="11"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>55001</v>
-      </c>
-      <c r="B12">
-        <v>60000</v>
-      </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="11"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>60001</v>
-      </c>
-      <c r="B13">
-        <v>65000</v>
-      </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="11"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>65001</v>
-      </c>
-      <c r="B14">
-        <v>70000</v>
-      </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="11"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>70001</v>
-      </c>
-      <c r="B15">
-        <v>75000</v>
-      </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="11"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>75001</v>
-      </c>
-      <c r="B16">
-        <v>80000</v>
-      </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="11"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>80001</v>
-      </c>
-      <c r="B17">
-        <v>85000</v>
-      </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="11"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>85001</v>
-      </c>
-      <c r="B18">
-        <v>90000</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="11"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>90001</v>
-      </c>
-      <c r="B19">
-        <v>95000</v>
-      </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="11"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>95001</v>
-      </c>
-      <c r="B20">
-        <v>100000</v>
-      </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="11"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>100001</v>
-      </c>
-      <c r="B21">
-        <v>120000</v>
-      </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="11"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>120001</v>
-      </c>
-      <c r="B22">
-        <v>150000</v>
-      </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="11"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>150001</v>
-      </c>
-      <c r="B23">
-        <v>200000</v>
-      </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="11"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>200001</v>
-      </c>
-      <c r="B24">
-        <v>300000</v>
-      </c>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="11"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>300001</v>
-      </c>
-      <c r="B25">
-        <v>400000</v>
-      </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="34"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="11"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>400001</v>
-      </c>
-      <c r="B26">
-        <v>500000</v>
-      </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="11"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>500001</v>
-      </c>
-      <c r="B27">
-        <v>1000000</v>
-      </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="34"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="11"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>1000001</v>
-      </c>
-      <c r="B28">
-        <v>2000000</v>
-      </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="11"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>2000001</v>
-      </c>
-      <c r="B29" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="34"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="11"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="29"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="N31" t="s">
-        <v>18</v>
-      </c>
-      <c r="O31" s="15"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B32" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="10">
-        <f>SUM(C4:C29)</f>
-        <v>0</v>
-      </c>
-      <c r="D32" s="10">
-        <f>SUM(D4:D29)</f>
-        <v>0</v>
-      </c>
-      <c r="I32" t="s">
-        <v>20</v>
-      </c>
-      <c r="J32" s="7"/>
-      <c r="N32" t="s">
-        <v>21</v>
-      </c>
-      <c r="O32" s="15"/>
-    </row>
-    <row r="33" spans="9:10" x14ac:dyDescent="0.35">
-      <c r="I33" t="s">
-        <v>1</v>
-      </c>
-      <c r="J33" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:Q1"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2687,7 +2723,7 @@
         <v>7</v>
       </c>
       <c r="I2" s="42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J2" s="43"/>
       <c r="K2" s="44"/>
@@ -2699,13 +2735,13 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="I3" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="17" t="s">
+      <c r="K3" s="18" t="s">
         <v>24</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>25</v>
       </c>
       <c r="M3" s="27"/>
     </row>
@@ -3080,7 +3116,7 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="K31" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
